--- a/model_info/det_gpt_domain.xlsx
+++ b/model_info/det_gpt_domain.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="6.6000000000000005" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="25.3" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="23.1" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.32</v>
+        <v>0.5565517241379311</v>
       </c>
     </row>
     <row r="2">
@@ -491,7 +491,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.4523809523809524</v>
+        <v>0.6949404761904762</v>
       </c>
     </row>
     <row r="4">
@@ -589,7 +589,7 @@
         <v>0.39758261400899414</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.6111111111111112</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
         <v>0.9776859672120618</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.625</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>1.0</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.8571428571428572</v>
+        <v>0.9285714285714286</v>
       </c>
     </row>
     <row r="8">
@@ -785,7 +785,7 @@
         <v>0.9</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.888888888888889</v>
+        <v>0.9444444444444444</v>
       </c>
     </row>
     <row r="10">
@@ -883,7 +883,7 @@
         <v>1.0</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.9090909090909092</v>
       </c>
     </row>
     <row r="12">
@@ -1030,7 +1030,7 @@
         <v>1.0</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.6</v>
+        <v>0.5247706422018348</v>
       </c>
     </row>
     <row r="15">
@@ -1177,7 +1177,7 @@
         <v>1.0</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>1.0</v>
+        <v>0.9473684210526316</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.16</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.053333333333333344</v>
+        <v>0.5042786069651741</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5637254901960784</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>1.0</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.9092063492063491</v>
+        <v>0.9046031746031746</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>1.0</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.9270833333333334</v>
+        <v>0.904718137254902</v>
       </c>
     </row>
     <row r="22">
@@ -1471,7 +1471,7 @@
         <v>1.0</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9613095238095238</v>
       </c>
     </row>
   </sheetData>

--- a/model_info/det_gpt_domain.xlsx
+++ b/model_info/det_gpt_domain.xlsx
@@ -344,7 +344,7 @@
     <col width="4.4" min="12" max="12" bestFit="1" customWidth="1"/>
     <col width="6.6000000000000005" min="13" max="13" bestFit="1" customWidth="1"/>
     <col width="24.200000000000003" min="14" max="14" bestFit="1" customWidth="1"/>
-    <col width="23.1" min="15" max="15" bestFit="1" customWidth="1"/>
+    <col width="24.200000000000003" min="15" max="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -393,7 +393,7 @@
         <v>0.36363636363636365</v>
       </c>
       <c r="O1" s="0" t="n">
-        <v>0.5565517241379311</v>
+        <v>0.2537931034482759</v>
       </c>
     </row>
     <row r="2">
@@ -491,7 +491,7 @@
         <v>0.7777777777777778</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>0.6949404761904762</v>
+        <v>0.42410714285714285</v>
       </c>
     </row>
     <row r="4">
@@ -589,7 +589,7 @@
         <v>0.39758261400899414</v>
       </c>
       <c r="O5" s="0" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.32407407407407407</v>
       </c>
     </row>
     <row r="6">
@@ -638,7 +638,7 @@
         <v>0.9776859672120618</v>
       </c>
       <c r="O6" s="0" t="n">
-        <v>0.8125</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="7">
@@ -687,7 +687,7 @@
         <v>1.0</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428572</v>
       </c>
     </row>
     <row r="8">
@@ -785,7 +785,7 @@
         <v>0.9</v>
       </c>
       <c r="O9" s="0" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.888888888888889</v>
       </c>
     </row>
     <row r="10">
@@ -883,7 +883,7 @@
         <v>1.0</v>
       </c>
       <c r="O11" s="0" t="n">
-        <v>0.9090909090909092</v>
+        <v>0.8181818181818182</v>
       </c>
     </row>
     <row r="12">
@@ -1030,7 +1030,7 @@
         <v>1.0</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>0.5247706422018348</v>
+        <v>0.2697247706422018</v>
       </c>
     </row>
     <row r="15">
@@ -1177,7 +1177,7 @@
         <v>1.0</v>
       </c>
       <c r="O17" s="0" t="n">
-        <v>0.9473684210526316</v>
+        <v>0.8947368421052632</v>
       </c>
     </row>
     <row r="18">
@@ -1226,7 +1226,7 @@
         <v>0.16</v>
       </c>
       <c r="O18" s="0" t="n">
-        <v>0.5042786069651741</v>
+        <v>0.05094527363184081</v>
       </c>
     </row>
     <row r="19">
@@ -1275,7 +1275,7 @@
         <v>0.4</v>
       </c>
       <c r="O19" s="0" t="n">
-        <v>0.5637254901960784</v>
+        <v>0.2647058823529412</v>
       </c>
     </row>
     <row r="20">
@@ -1324,7 +1324,7 @@
         <v>1.0</v>
       </c>
       <c r="O20" s="0" t="n">
-        <v>0.9046031746031746</v>
+        <v>0.8182857142857143</v>
       </c>
     </row>
     <row r="21">
@@ -1373,7 +1373,7 @@
         <v>1.0</v>
       </c>
       <c r="O21" s="0" t="n">
-        <v>0.904718137254902</v>
+        <v>0.8180147058823529</v>
       </c>
     </row>
     <row r="22">
@@ -1471,7 +1471,7 @@
         <v>1.0</v>
       </c>
       <c r="O23" s="0" t="n">
-        <v>0.9613095238095238</v>
+        <v>0.9226190476190477</v>
       </c>
     </row>
   </sheetData>
